--- a/ecuacion-tool-housekeep-db/excel-format/housekeep-db_fmt-v2.0.0-ja_sample.xlsx
+++ b/ecuacion-tool-housekeep-db/excel-format/housekeep-db_fmt-v2.0.0-ja_sample.xlsx
@@ -513,10 +513,10 @@
     <t>データ検索条件設定</t>
   </si>
   <si>
-    <t>論理廃止 / 削除</t>
-  </si>
-  <si>
-    <t>論理廃止 / 削除（内部値）</t>
+    <t>処理種別</t>
+  </si>
+  <si>
+    <t>処理種別（内部値）</t>
   </si>
   <si>
     <t>関連テーブル処理パターン（内部値）</t>
@@ -529,7 +529,10 @@
 ・infoシート
 　- database項目削除（mysqlへの対応追加に伴う修正）
 　- 非表示に変更
-　- 1行目のコメントを削除</t>
+　- 1行目のコメントを削除
+・housekeep DB設定 シート
+　- 「論理廃止 / 削除」列を「処理種別」に名称変更（内部値の列も同様）
+　- 処理種別の選択肢に「異常データ存在チェック」を追加</t>
   </si>
   <si>
     <t>2.0.0</t>
@@ -1919,9 +1922,9 @@
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{CBD51E9F-618C-754C-8BA6-0B46FCE3F82F}" name="処理ID" dataDxfId="53"/>
     <tableColumn id="12" xr3:uid="{5E33A481-4C3C-A049-B253-3EC944DDB6EC}" name="DB接続ID" dataDxfId="52" dataCellStyle="標準 2"/>
-    <tableColumn id="2" xr3:uid="{AADC801E-ABC4-9E4F-8EFF-3383030B2A4B}" name="論理廃止 / 削除" dataDxfId="51"/>
-    <tableColumn id="15" xr3:uid="{F58118F0-6716-6C42-853A-3FBAEE07F4E8}" name="論理廃止 / 削除（内部値）" dataDxfId="50">
-      <calculatedColumnFormula array="1">_xlfn.IFS(テーブル32[[#This Row],[論理廃止 / 削除]]="論理廃止","SOFT_DELETE",テーブル32[[#This Row],[論理廃止 / 削除]]="削除","HARD_DELETE",TRUE,"")</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{AADC801E-ABC4-9E4F-8EFF-3383030B2A4B}" name="処理種別" dataDxfId="51"/>
+    <tableColumn id="15" xr3:uid="{F58118F0-6716-6C42-853A-3FBAEE07F4E8}" name="処理種別（内部値）" dataDxfId="50">
+      <calculatedColumnFormula array="1">_xlfn.IFS(テーブル32[[#This Row],[処理種別]]="論理廃止","SOFT_DELETE",テーブル32[[#This Row],[処理種別]]="削除","HARD_DELETE",テーブル32[[#This Row],[処理種別]]="異常データ存在チェック","ABNORMAL_DATA_CHECK",TRUE,"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{6C98AD64-A3D3-F44E-A881-8EFCEA1F9F67}" name="テーブル名" dataDxfId="49" dataCellStyle="標準 2"/>
     <tableColumn id="4" xr3:uid="{A38A3149-447A-8548-9729-49CE9E074B36}" name="IDカラム名" dataDxfId="48" dataCellStyle="標準 2"/>
@@ -2379,7 +2382,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="112" x14ac:dyDescent="0.2">
       <c r="A9" s="17">
         <v>46256</v>
       </c>
@@ -2742,7 +2745,7 @@
       <c r="A5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8" t="str" cm="1">
-        <f t="array" ref="D5">_xlfn.IFS(テーブル32[[#This Row],[論理廃止 / 削除]]="論理廃止","SOFT_DELETE",テーブル32[[#This Row],[論理廃止 / 削除]]="削除","HARD_DELETE",TRUE,"")</f>
+        <f t="array" ref="D5">_xlfn.IFS(テーブル32[[#This Row],[処理種別]]="論理廃止","SOFT_DELETE",テーブル32[[#This Row],[処理種別]]="削除","HARD_DELETE",テーブル32[[#This Row],[処理種別]]="異常データ存在チェック","ABNORMAL_DATA_CHECK",TRUE,"")</f>
         <v/>
       </c>
       <c r="E5" s="8"/>
@@ -2771,7 +2774,7 @@
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{8F6F98C1-595C-9F49-B250-21CD2634841D}">
-      <formula1>"論理廃止,削除"</formula1>
+      <formula1>"論理廃止,削除,異常データ存在チェック"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5 N5" xr:uid="{7B8B2790-6C59-604D-89F1-3BD24DE216A5}">
       <formula1>"quotes('),(none)"</formula1>

--- a/ecuacion-tool-housekeep-db/excel-format/housekeep-db_fmt-v2.0.0-ja_sample.xlsx
+++ b/ecuacion-tool-housekeep-db/excel-format/housekeep-db_fmt-v2.0.0-ja_sample.xlsx
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="80">
   <si>
     <t>value</t>
     <phoneticPr fontId="1"/>
@@ -532,7 +532,9 @@
 　- 1行目のコメントを削除
 ・housekeep DB設定 シート
 　- 「論理廃止 / 削除」列を「処理種別」に名称変更（内部値の列も同様）
-　- 処理種別の選択肢に「異常データ存在チェック」を追加</t>
+　- 処理種別の選択肢に「異常データ存在チェック」を追加
+・データ検索条件設定 シート
+　- 「条件演算子」列を追加（equal / not equal）</t>
   </si>
   <si>
     <t>2.0.0</t>
@@ -542,6 +544,9 @@
   </si>
   <si>
     <t>論理廃止用項目</t>
+  </si>
+  <si>
+    <t>条件演算子</t>
   </si>
 </sst>
 </file>
@@ -1943,11 +1948,12 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DBD8E589-22D9-8541-A9D6-F03C8FC47C4E}" name="テーブル323" displayName="テーブル323" ref="A4:D5" insertRow="1" totalsRowShown="0" headerRowDxfId="18">
-  <autoFilter ref="A4:D5" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DBD8E589-22D9-8541-A9D6-F03C8FC47C4E}" name="テーブル323" displayName="テーブル323" ref="A4:E5" insertRow="1" totalsRowShown="0" headerRowDxfId="18">
+  <autoFilter ref="A4:E5" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{0B02141A-0F5F-8849-982C-6C0A6A7BEE4F}" name="処理ID" dataDxfId="17" dataCellStyle="標準 2"/>
     <tableColumn id="12" xr3:uid="{69A08ECC-4076-9E48-8CE9-3FABB073CA81}" name="条件カラム名" dataDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{6E5A0673-F7B6-4381-8294-0F4068A241E9}" name="条件演算子" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{511F37DB-74E3-394C-9204-B1C6CA623CD0}" name="条件カラム型リテラル記号" dataDxfId="15"/>
     <tableColumn id="3" xr3:uid="{2F474AF9-6428-D446-9D8C-0FEF2C86FE1D}" name="条件カラム値" dataDxfId="14" dataCellStyle="標準 2"/>
   </tableColumns>
@@ -2382,7 +2388,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="144" x14ac:dyDescent="0.2">
       <c r="A9" s="17">
         <v>46256</v>
       </c>
@@ -2806,56 +2812,65 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E1BEA4-8682-2D4B-83F3-E3D5D9773981}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.5" style="6" customWidth="1"/>
     <col min="2" max="2" width="23.83203125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="25.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" style="6" customWidth="1"/>
-    <col min="5" max="16384" width="7.5" style="6"/>
+    <col min="3" max="3" width="22" style="6" customWidth="1"/>
+    <col min="4" max="4" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="7.5" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="E4" s="33" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D5" s="8"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
-      <c r="D6" s="7"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C6" xr:uid="{F3EDCD97-3DDD-0A4D-ACDF-687A95CDC907}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D6" xr:uid="{F3EDCD97-3DDD-0A4D-ACDF-687A95CDC907}">
       <formula1>"quotes('),(none)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C6" xr:uid="{95E99013-DC8A-4921-B883-052B0E90F976}">
+      <formula1>"equal,not equal"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ecuacion-tool-housekeep-db/excel-format/housekeep-db_fmt-v2.0.0-ja_sample.xlsx
+++ b/ecuacion-tool-housekeep-db/excel-format/housekeep-db_fmt-v2.0.0-ja_sample.xlsx
@@ -347,7 +347,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>論理廃止：更新用timestampカラム名</t>
+    <t>論理廃止：更新用日付／日時カラム名</t>
     <rPh sb="5" eb="7">
       <t xml:space="preserve">コウシンヨウ </t>
     </rPh>
@@ -434,13 +434,13 @@
 ・空欄だと分かりにくいので「(none)」を入れる方式は、そちらの方が面倒だしどうせテストするので不要なことから空欄へ変更</t>
   </si>
   <si>
-    <t>期間経過チェック用：timestampカラム名</t>
+    <t>期間経過チェック用：日付／日時カラム名</t>
   </si>
   <si>
     <t>期間経過チェック用：timestampカラム型</t>
   </si>
   <si>
-    <t>期間経過チェック用：timestamp要経過日数</t>
+    <t>期間経過チェック用：要経過日数</t>
   </si>
   <si>
     <t>削除フラグカラム名</t>
@@ -464,7 +464,7 @@
     <t>論理廃止：更新用ユーザIDカラム型リテラル記号</t>
   </si>
   <si>
-    <t>論理廃止：更新用timestampカラム名</t>
+    <t>論理廃止：更新用日付／日時カラム名</t>
   </si>
   <si>
     <t>locale</t>
@@ -534,7 +534,11 @@
 　- 「論理廃止 / 削除」列を「処理種別」に名称変更（内部値の列も同様）
 　- 処理種別の選択肢に「異常データ存在チェック」を追加
 ・データ検索条件設定 シート
-　- 「条件演算子」列を追加（equal / not equal）</t>
+　- 「条件演算子」列を追加（equal / not equal）
+・日付型の列も指定できるようになったため、項目名から「timestamp」を除く変更
+　- 期間経過チェック用：timestampカラム名 -&gt; 期間経過チェック用：日付／日時カラム名
+　- 期間経過チェック用：timestamp要経過日数 -&gt; 期間経過チェック用：要経過日数
+　- 論理廃止：更新用timestampカラム名 -&gt; 論理廃止：更新用日付／日時カラム名（関連テーブル処理設定 シートも同様）</t>
   </si>
   <si>
     <t>2.0.0</t>
@@ -1934,11 +1938,11 @@
     <tableColumn id="3" xr3:uid="{6C98AD64-A3D3-F44E-A881-8EFCEA1F9F67}" name="テーブル名" dataDxfId="49" dataCellStyle="標準 2"/>
     <tableColumn id="4" xr3:uid="{A38A3149-447A-8548-9729-49CE9E074B36}" name="IDカラム名" dataDxfId="48" dataCellStyle="標準 2"/>
     <tableColumn id="10" xr3:uid="{B15AF0F8-272C-B943-9D75-81A8797BC598}" name="IDカラム型リテラル記号" dataDxfId="47"/>
-    <tableColumn id="5" xr3:uid="{6FE6A1FF-15C9-7545-B254-7B2C29EF168D}" name="期間経過チェック用：timestampカラム名" dataDxfId="46" dataCellStyle="標準 2"/>
+    <tableColumn id="5" xr3:uid="{6FE6A1FF-15C9-7545-B254-7B2C29EF168D}" name="期間経過チェック用：日付／日時カラム名" dataDxfId="46" dataCellStyle="標準 2"/>
     <tableColumn id="11" xr3:uid="{BF075527-A2E7-834B-AD05-1A2D9E3BA0AD}" name="期間経過チェック用：timestampカラム型" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{94EB7746-8D75-EE47-A2F3-81D397D26AE1}" name="期間経過チェック用：timestamp要経過日数" dataDxfId="44" dataCellStyle="標準 2"/>
+    <tableColumn id="6" xr3:uid="{94EB7746-8D75-EE47-A2F3-81D397D26AE1}" name="期間経過チェック用：要経過日数" dataDxfId="44" dataCellStyle="標準 2"/>
     <tableColumn id="7" xr3:uid="{62ADB4F3-1C59-7F4B-819E-B49B0ABB889C}" name="削除フラグカラム名" dataDxfId="43" dataCellStyle="標準 2"/>
-    <tableColumn id="8" xr3:uid="{0EB6A694-7E00-B64C-AF69-22B6C7E1C560}" name="論理廃止：更新用timestampカラム名" dataDxfId="42" dataCellStyle="標準 2"/>
+    <tableColumn id="8" xr3:uid="{0EB6A694-7E00-B64C-AF69-22B6C7E1C560}" name="論理廃止：更新用日付／日時カラム名" dataDxfId="42" dataCellStyle="標準 2"/>
     <tableColumn id="9" xr3:uid="{0A6924E1-C0CB-AF40-A208-E0E96A257245}" name="論理廃止：更新用ユーザIDカラム名" dataDxfId="41" dataCellStyle="標準 2"/>
     <tableColumn id="14" xr3:uid="{93BF3B4F-D2E8-A640-A768-A230439878D9}" name="論理廃止：更新用ユーザIDカラム型リテラル記号" dataDxfId="40" dataCellStyle="標準 2"/>
     <tableColumn id="13" xr3:uid="{DE6ACC44-9137-0840-9711-E0D04FCC851F}" name="論理廃止：更新用ユーザIDカラム値" dataDxfId="39" dataCellStyle="標準 2"/>
@@ -1975,7 +1979,7 @@
     <tableColumn id="3" xr3:uid="{59ED585B-1BCF-DB41-A333-2655E74C710D}" name="関連テーブルIDカラム名" dataDxfId="6" dataCellStyle="標準 2"/>
     <tableColumn id="14" xr3:uid="{75144EA6-AFC2-3646-9A0E-DD4A2D917411}" name="関連テーブルIDカラム型リテラル記号" dataDxfId="5" dataCellStyle="標準 2"/>
     <tableColumn id="4" xr3:uid="{684AF203-54CE-5A42-8441-2636BF604DAF}" name="削除フラグカラム名" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{1D070257-74D6-6746-B460-ACB59A1770E6}" name="論理廃止：更新用timestampカラム名" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{1D070257-74D6-6746-B460-ACB59A1770E6}" name="論理廃止：更新用日付／日時カラム名" dataDxfId="3"/>
     <tableColumn id="6" xr3:uid="{59287FEB-061F-B946-B814-312CDD2F482D}" name="論理廃止：更新用ユーザIDカラム名" dataDxfId="2"/>
     <tableColumn id="7" xr3:uid="{E0734288-8DC3-C342-98A6-DBC50A55CEF9}" name="論理廃止：更新用ユーザIDカラム型リテラル記号" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{D5E8A958-B06D-554D-B183-49DD307AC86A}" name="論理廃止：更新用ユーザIDカラム値" dataDxfId="0"/>
@@ -2388,7 +2392,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="144" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="224" x14ac:dyDescent="0.2">
       <c r="A9" s="17">
         <v>46256</v>
       </c>

--- a/ecuacion-tool-housekeep-db/excel-format/housekeep-db_fmt-v2.0.0-ja_sample.xlsx
+++ b/ecuacion-tool-housekeep-db/excel-format/housekeep-db_fmt-v2.0.0-ja_sample.xlsx
@@ -538,7 +538,9 @@
 ・日付型の列も指定できるようになったため、項目名から「timestamp」を除く変更
 　- 期間経過チェック用：timestampカラム名 -&gt; 期間経過チェック用：日付／日時カラム名
 　- 期間経過チェック用：timestamp要経過日数 -&gt; 期間経過チェック用：要経過日数
-　- 論理廃止：更新用timestampカラム名 -&gt; 論理廃止：更新用日付／日時カラム名（関連テーブル処理設定 シートも同様）</t>
+　- 論理廃止：更新用timestampカラム名 -&gt; 論理廃止：更新用日付／日時カラム名（関連テーブル処理設定 シートも同様）
+・housekeep DB設定 シート
+　- 「期間経過チェック用：timestampカラム型」列を削除（SQLの生成に使われておらず不要なため）</t>
   </si>
   <si>
     <t>2.0.0</t>
@@ -1926,9 +1928,9 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61C29F33-44CC-B14C-8562-09C29609B4D7}" name="テーブル32" displayName="テーブル32" ref="A4:O5" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
-  <autoFilter ref="A4:O5" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61C29F33-44CC-B14C-8562-09C29609B4D7}" name="テーブル32" displayName="テーブル32" ref="A4:N5" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+  <autoFilter ref="A4:N5" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{CBD51E9F-618C-754C-8BA6-0B46FCE3F82F}" name="処理ID" dataDxfId="53"/>
     <tableColumn id="12" xr3:uid="{5E33A481-4C3C-A049-B253-3EC944DDB6EC}" name="DB接続ID" dataDxfId="52" dataCellStyle="標準 2"/>
     <tableColumn id="2" xr3:uid="{AADC801E-ABC4-9E4F-8EFF-3383030B2A4B}" name="処理種別" dataDxfId="51"/>
@@ -1939,7 +1941,6 @@
     <tableColumn id="4" xr3:uid="{A38A3149-447A-8548-9729-49CE9E074B36}" name="IDカラム名" dataDxfId="48" dataCellStyle="標準 2"/>
     <tableColumn id="10" xr3:uid="{B15AF0F8-272C-B943-9D75-81A8797BC598}" name="IDカラム型リテラル記号" dataDxfId="47"/>
     <tableColumn id="5" xr3:uid="{6FE6A1FF-15C9-7545-B254-7B2C29EF168D}" name="期間経過チェック用：日付／日時カラム名" dataDxfId="46" dataCellStyle="標準 2"/>
-    <tableColumn id="11" xr3:uid="{BF075527-A2E7-834B-AD05-1A2D9E3BA0AD}" name="期間経過チェック用：timestampカラム型" dataDxfId="45"/>
     <tableColumn id="6" xr3:uid="{94EB7746-8D75-EE47-A2F3-81D397D26AE1}" name="期間経過チェック用：要経過日数" dataDxfId="44" dataCellStyle="標準 2"/>
     <tableColumn id="7" xr3:uid="{62ADB4F3-1C59-7F4B-819E-B49B0ABB889C}" name="削除フラグカラム名" dataDxfId="43" dataCellStyle="標準 2"/>
     <tableColumn id="8" xr3:uid="{0EB6A694-7E00-B64C-AF69-22B6C7E1C560}" name="論理廃止：更新用日付／日時カラム名" dataDxfId="42" dataCellStyle="標準 2"/>
@@ -2392,7 +2393,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="224" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="256" x14ac:dyDescent="0.2">
       <c r="A9" s="17">
         <v>46256</v>
       </c>
@@ -2476,9 +2477,7 @@
       <c r="B1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="C1" s="9"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
@@ -2487,18 +2486,14 @@
       <c r="B2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>23</v>
-      </c>
+      <c r="C2" s="10"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="10"/>
       <c r="B3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>22</v>
-      </c>
+      <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="10"/>
@@ -2662,7 +2657,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{789F72C4-22B4-0242-AA9D-05DCD1C7C1AF}">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.5" style="6" customWidth="1"/>
@@ -2671,23 +2666,23 @@
     <col min="4" max="4" width="25.6640625" style="6" hidden="1" customWidth="1"/>
     <col min="5" max="6" width="20.1640625" style="6" customWidth="1"/>
     <col min="7" max="7" width="25.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="38" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="44.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="33.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="44.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="33.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="7.5" style="6"/>
+    <col min="8" max="8" width="38" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="44.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="33.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="44.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="33.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="7.5" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>26</v>
       </c>
@@ -2695,16 +2690,15 @@
         <v>77</v>
       </c>
       <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="35" t="s">
+      <c r="J3" s="35" t="s">
         <v>78</v>
       </c>
+      <c r="K3" s="35"/>
       <c r="L3" s="35"/>
       <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="36"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N3" s="36"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="26" t="s">
         <v>62</v>
       </c>
@@ -2730,28 +2724,25 @@
         <v>50</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" s="28" t="s">
         <v>52</v>
       </c>
+      <c r="J4" s="29" t="s">
+        <v>53</v>
+      </c>
       <c r="K4" s="29" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L4" s="29" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M4" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="N4" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="O4" s="30" t="s">
+      <c r="N4" s="30" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8" t="str" cm="1">
@@ -2764,33 +2755,29 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="N5" s="8"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M5" s="8"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="19"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="19"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:O3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:N3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{8F6F98C1-595C-9F49-B250-21CD2634841D}">
       <formula1>"論理廃止,削除,異常データ存在チェック"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5 N5" xr:uid="{7B8B2790-6C59-604D-89F1-3BD24DE216A5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5 M5" xr:uid="{7B8B2790-6C59-604D-89F1-3BD24DE216A5}">
       <formula1>"quotes('),(none)"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5" xr:uid="{77C8DCE9-D337-B146-99D9-21A4944967AD}">
-      <formula1>"LocalDateTime,OffsetDateTime"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2806,7 +2793,7 @@
           <x14:formula1>
             <xm:f>dropdown!$B$2:$B$20</xm:f>
           </x14:formula1>
-          <xm:sqref>N6</xm:sqref>
+          <xm:sqref>M6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/ecuacion-tool-housekeep-db/excel-format/housekeep-db_fmt-v2.0.0-ja_sample.xlsx
+++ b/ecuacion-tool-housekeep-db/excel-format/housekeep-db_fmt-v2.0.0-ja_sample.xlsx
@@ -20,6 +20,7 @@
     <sheet name="housekeep DB設定" sheetId="10" r:id="rId5"/>
     <sheet name="データ検索条件設定" sheetId="12" r:id="rId6"/>
     <sheet name="関連テーブル処理設定" sheetId="14" r:id="rId7"/>
+    <sheet name="更新項目設定" sheetId="16" r:id="rId15"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId8"/>
@@ -89,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="86">
   <si>
     <t>value</t>
     <phoneticPr fontId="1"/>
@@ -540,7 +541,9 @@
 　- 期間経過チェック用：timestamp要経過日数 -&gt; 期間経過チェック用：要経過日数
 　- 論理廃止：更新用timestampカラム名 -&gt; 論理廃止：更新用日付／日時カラム名（関連テーブル処理設定 シートも同様）
 ・housekeep DB設定 シート
-　- 「期間経過チェック用：timestampカラム型」列を削除（SQLの生成に使われておらず不要なため）</t>
+　- 「期間経過チェック用：timestampカラム型」列を削除（SQLの生成に使われておらず不要なため）
+　- 処理種別の選択肢に「更新」を追加
+・更新項目設定 シートを追加（処理種別が「更新」のタスクで書き換える列と値を設定）</t>
   </si>
   <si>
     <t>2.0.0</t>
@@ -553,6 +556,24 @@
   </si>
   <si>
     <t>条件演算子</t>
+  </si>
+  <si>
+    <t>更新項目設定</t>
+  </si>
+  <si>
+    <t>更新カラム名</t>
+  </si>
+  <si>
+    <t>更新値種別</t>
+  </si>
+  <si>
+    <t>更新値種別（内部値）</t>
+  </si>
+  <si>
+    <t>更新カラム型リテラル記号</t>
+  </si>
+  <si>
+    <t>更新カラム値</t>
   </si>
 </sst>
 </file>
@@ -1935,7 +1956,7 @@
     <tableColumn id="12" xr3:uid="{5E33A481-4C3C-A049-B253-3EC944DDB6EC}" name="DB接続ID" dataDxfId="52" dataCellStyle="標準 2"/>
     <tableColumn id="2" xr3:uid="{AADC801E-ABC4-9E4F-8EFF-3383030B2A4B}" name="処理種別" dataDxfId="51"/>
     <tableColumn id="15" xr3:uid="{F58118F0-6716-6C42-853A-3FBAEE07F4E8}" name="処理種別（内部値）" dataDxfId="50">
-      <calculatedColumnFormula array="1">_xlfn.IFS(テーブル32[[#This Row],[処理種別]]="論理廃止","SOFT_DELETE",テーブル32[[#This Row],[処理種別]]="削除","HARD_DELETE",テーブル32[[#This Row],[処理種別]]="異常データ存在チェック","ABNORMAL_DATA_CHECK",TRUE,"")</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.IFS(テーブル32[[#This Row],[処理種別]]="論理廃止","SOFT_DELETE",テーブル32[[#This Row],[処理種別]]="削除","HARD_DELETE",テーブル32[[#This Row],[処理種別]]="異常データ存在チェック","ABNORMAL_DATA_CHECK",テーブル32[[#This Row],[処理種別]]="更新","UPDATE",TRUE,"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{6C98AD64-A3D3-F44E-A881-8EFCEA1F9F67}" name="テーブル名" dataDxfId="49" dataCellStyle="標準 2"/>
     <tableColumn id="4" xr3:uid="{A38A3149-447A-8548-9729-49CE9E074B36}" name="IDカラム名" dataDxfId="48" dataCellStyle="標準 2"/>
@@ -1984,6 +2005,23 @@
     <tableColumn id="6" xr3:uid="{59287FEB-061F-B946-B814-312CDD2F482D}" name="論理廃止：更新用ユーザIDカラム名" dataDxfId="2"/>
     <tableColumn id="7" xr3:uid="{E0734288-8DC3-C342-98A6-DBC50A55CEF9}" name="論理廃止：更新用ユーザIDカラム型リテラル記号" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{D5E8A958-B06D-554D-B183-49DD307AC86A}" name="論理廃止：更新用ユーザIDカラム値" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{31B89BDC-3CC6-4DD3-BE32-9A28850B2E61}" name="テーブル7" displayName="テーブル7" ref="A4:F5" insertRow="1" totalsRowShown="0" headerRowDxfId="18">
+  <autoFilter ref="A4:F5" xr:uid="{84CDA143-0714-4713-8F2C-8E2ADB62D176}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{D9FB13E7-283E-4973-9D8F-AD7FC2EC6473}" name="処理ID" dataDxfId="17" dataCellStyle="標準 2"/>
+    <tableColumn id="2" xr3:uid="{4B0B84B8-778E-4917-B2A1-D58F4765B69F}" name="更新カラム名" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{AA8CE8B6-8F33-4C49-8B1C-D0975AA57F68}" name="更新値種別" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{31F8B758-90FF-4085-8587-8CB96AC32A8B}" name="更新値種別（内部値）" dataDxfId="16">
+      <calculatedColumnFormula array="1">_xlfn.IFS(テーブル7[[#This Row],[更新値種別]]="固定値","FIXED_VALUE",テーブル7[[#This Row],[更新値種別]]="現在日時","CURRENT_TIMESTAMP",テーブル7[[#This Row],[更新値種別]]="NULL","NULL",TRUE,"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{94F653A5-DD8B-491C-9AB4-1D4B7D196DB6}" name="更新カラム型リテラル記号" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{96E6F231-ED88-4FB0-85D3-7E553B0DBFE9}" name="更新カラム値" dataDxfId="14" dataCellStyle="標準 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2393,7 +2431,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="256" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="288" x14ac:dyDescent="0.2">
       <c r="A9" s="17">
         <v>46256</v>
       </c>
@@ -2746,7 +2784,7 @@
       <c r="A5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8" t="str" cm="1">
-        <f t="array" ref="D5">_xlfn.IFS(テーブル32[[#This Row],[処理種別]]="論理廃止","SOFT_DELETE",テーブル32[[#This Row],[処理種別]]="削除","HARD_DELETE",テーブル32[[#This Row],[処理種別]]="異常データ存在チェック","ABNORMAL_DATA_CHECK",TRUE,"")</f>
+        <f t="array" ref="D5">_xlfn.IFS(テーブル32[[#This Row],[処理種別]]="論理廃止","SOFT_DELETE",テーブル32[[#This Row],[処理種別]]="削除","HARD_DELETE",テーブル32[[#This Row],[処理種別]]="異常データ存在チェック","ABNORMAL_DATA_CHECK",テーブル32[[#This Row],[処理種別]]="更新","UPDATE",TRUE,"")</f>
         <v/>
       </c>
       <c r="E5" s="8"/>
@@ -2774,7 +2812,7 @@
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{8F6F98C1-595C-9F49-B250-21CD2634841D}">
-      <formula1>"論理廃止,削除,異常データ存在チェック"</formula1>
+      <formula1>"論理廃止,削除,異常データ存在チェック,更新"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5 M5" xr:uid="{7B8B2790-6C59-604D-89F1-3BD24DE216A5}">
       <formula1>"quotes('),(none)"</formula1>
@@ -3016,4 +3054,83 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E8E68B6-2E08-48F9-BBA8-C0A604BCABE6}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="40.5" style="6" customWidth="1"/>
+    <col min="2" max="2" width="23.83203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="22" style="6" customWidth="1"/>
+    <col min="4" max="4" width="25.5" style="6" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="28" style="6" customWidth="1"/>
+    <col min="6" max="6" width="22" style="6" customWidth="1"/>
+    <col min="7" max="16384" width="7.5" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8" t="str" cm="1">
+        <f t="array" ref="D5">_xlfn.IFS(テーブル7[[#This Row],[更新値種別]]="固定値","FIXED_VALUE",テーブル7[[#This Row],[更新値種別]]="現在日時","CURRENT_TIMESTAMP",テーブル7[[#This Row],[更新値種別]]="NULL","NULL",TRUE,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C6" xr:uid="{41994EA3-6DC0-41E7-9190-0288E0543431}">
+      <formula1>"固定値,現在日時,NULL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E6" xr:uid="{38776FA8-26CC-4B28-988A-ECF295377112}">
+      <formula1>"quotes('),(none)"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>